--- a/Demo/MDA/demo_mda_9999_6_supervision_CDD.xlsx
+++ b/Demo/MDA/demo_mda_9999_6_supervision_CDD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\Demo\MDA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{931638EF-5038-4161-B740-73B017A01746}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB67932A-07AA-4A9A-BFFD-04E398290E2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -864,9 +864,6 @@
 not(selected(${s_medicine}, 'TETRA') and not(selected(${s_disease}, 'TRACHOMA')))</t>
   </si>
   <si>
-    <t>selected(${s_disease}, disease_filter)</t>
-  </si>
-  <si>
     <t>Challenges encountered</t>
   </si>
   <si>
@@ -910,6 +907,9 @@
   </si>
   <si>
     <t>demo_mda_9999_6_supervision_CDD_v3</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> selected(${s_disease}, disease_filter)</t>
   </si>
 </sst>
 </file>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="K10" s="16"/>
       <c r="L10" s="27" t="s">
-        <v>259</v>
+        <v>274</v>
       </c>
       <c r="M10" s="16"/>
       <c r="N10" s="16"/>
@@ -1839,10 +1839,10 @@
         <v>10</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D15" s="23"/>
       <c r="E15" s="23" t="s">
@@ -1950,7 +1950,7 @@
         <v>164</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D19" s="6"/>
       <c r="E19" s="5"/>
@@ -2054,7 +2054,7 @@
         <v>235</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D23" s="6"/>
       <c r="E23" s="5"/>
@@ -2081,7 +2081,7 @@
         <v>236</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D24" s="6"/>
       <c r="E24" s="5"/>
@@ -2108,7 +2108,7 @@
         <v>237</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D25" s="6"/>
       <c r="E25" s="5"/>
@@ -2135,7 +2135,7 @@
         <v>238</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D26" s="6"/>
       <c r="E26" s="5"/>
@@ -2189,7 +2189,7 @@
         <v>241</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D28" s="6"/>
       <c r="E28" s="5"/>
@@ -2216,7 +2216,7 @@
         <v>242</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D29" s="6"/>
       <c r="E29" s="5"/>
@@ -2428,7 +2428,7 @@
         <v>223</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="5"/>
@@ -2455,7 +2455,7 @@
         <v>224</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D38" s="6"/>
       <c r="E38" s="5"/>
@@ -2555,7 +2555,7 @@
         <v>61</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D42" s="6"/>
       <c r="E42" s="5"/>
@@ -2582,7 +2582,7 @@
         <v>62</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D43" s="6"/>
       <c r="E43" s="5"/>
@@ -2609,7 +2609,7 @@
         <v>63</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D44" s="6"/>
       <c r="E44" s="5"/>
@@ -2720,7 +2720,7 @@
         <v>21</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E1" s="25" t="s">
         <v>64</v>
@@ -4776,7 +4776,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25.28515625" bestFit="1" customWidth="1"/>
   </cols>
@@ -4795,10 +4795,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B2" t="s">
         <v>273</v>
-      </c>
-      <c r="B2" t="s">
-        <v>274</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>
